--- a/data/trans_dic/IP1020-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP1020-Clase-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que padecen transtornos crónicos de la piel</t>
+          <t>Menores que padecen transtornos crónicos de la piel (tasa de respuesta: 99,82%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,6; 4,96</t>
+          <t>0,6; 5,55</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,55</t>
+          <t>0,0; 4,59</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,76; 7,05</t>
+          <t>0,74; 6,98</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2,14; 9,58</t>
+          <t>2,13; 9,59</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,86</t>
+          <t>0,0; 3,06</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,06</t>
+          <t>0,0; 4,39</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,17; 8,1</t>
+          <t>1,33; 7,94</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1,17; 7,6</t>
+          <t>1,24; 6,86</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,31; 3,15</t>
+          <t>0,32; 3,11</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,37; 3,57</t>
+          <t>0,36; 3,24</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1,59; 5,86</t>
+          <t>1,61; 5,94</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>2,16; 6,56</t>
+          <t>2,11; 6,65</t>
         </is>
       </c>
     </row>
@@ -856,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0; 1,46</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,72; 5,75</t>
+          <t>0,73; 6,91</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0; 1,22</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,25; 8,16</t>
+          <t>1,23; 7,78</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,04</t>
+          <t>0,0; 2,86</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0; 1,37</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,59; 5,83</t>
+          <t>0,59; 6,04</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,74; 6,15</t>
+          <t>0,0; 6,32</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,4</t>
+          <t>0,0; 1,57</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,36; 3,12</t>
+          <t>0,36; 3,17</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,3; 3,16</t>
+          <t>0,3; 3,36</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,31; 5,54</t>
+          <t>1,29; 5,68</t>
         </is>
       </c>
     </row>
@@ -996,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,55</t>
+          <t>0,0; 8,45</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,74; 6,91</t>
+          <t>0,74; 6,28</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 2,0</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,23</t>
+          <t>0,0; 9,83</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,81</t>
+          <t>0,0; 4,82</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,66</t>
+          <t>0,0; 3,51</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,37</t>
+          <t>0,0; 6,48</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,74; 9,25</t>
+          <t>0,73; 8,86</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,4; 3,6</t>
+          <t>0,4; 3,37</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,4; 3,63</t>
+          <t>0,39; 3,49</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,04</t>
+          <t>0,0; 3,42</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,96; 6,49</t>
+          <t>1,06; 6,71</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,47</t>
+          <t>0,0; 1,46</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,85; 4,16</t>
+          <t>0,88; 4,59</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,71; 3,59</t>
+          <t>0,93; 3,95</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,32; 5,59</t>
+          <t>1,41; 5,8</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,32; 2,9</t>
+          <t>0,32; 3,34</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,27; 2,43</t>
+          <t>0,27; 2,41</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,43</t>
+          <t>0,0; 2,28</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,51; 6,25</t>
+          <t>1,63; 6,06</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,17; 1,68</t>
+          <t>0,17; 1,49</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0,78; 2,95</t>
+          <t>0,61; 2,66</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,59; 2,46</t>
+          <t>0,59; 2,31</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1,82; 4,91</t>
+          <t>1,93; 5,03</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,27</t>
+          <t>0,0; 3,72</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,93; 5,86</t>
+          <t>0,97; 5,27</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,66</t>
+          <t>0,0; 3,77</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,32; 6,95</t>
+          <t>1,28; 6,94</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,58</t>
+          <t>0,0; 3,6</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,52; 4,88</t>
+          <t>0,51; 4,72</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,14</t>
+          <t>0,0; 2,82</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>1,03; 5,83</t>
+          <t>1,19; 6,04</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,27; 2,44</t>
+          <t>0,27; 2,59</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1,11; 4,06</t>
+          <t>1,13; 4,17</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,24; 2,46</t>
+          <t>0,24; 2,41</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>1,47; 4,98</t>
+          <t>1,63; 5,18</t>
         </is>
       </c>
     </row>
@@ -1416,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,22</t>
+          <t>0,0; 6,61</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1,36; 12,47</t>
+          <t>1,34; 12,33</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,33</t>
+          <t>0,0; 5,19</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,84</t>
+          <t>0,0; 12,19</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 1,74</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,62; 7,15</t>
+          <t>0,62; 7,72</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,93; 7,58</t>
+          <t>0,93; 8,66</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1,18; 11,04</t>
+          <t>1,25; 11,36</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,23</t>
+          <t>0,0; 2,93</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1,55; 7,45</t>
+          <t>1,67; 7,57</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0,5; 4,53</t>
+          <t>0,5; 5,07</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>1,62; 8,35</t>
+          <t>1,62; 8,12</t>
         </is>
       </c>
     </row>
@@ -1556,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,41; 1,59</t>
+          <t>0,33; 1,6</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,59; 3,56</t>
+          <t>1,64; 3,63</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,7; 2,05</t>
+          <t>0,74; 2,11</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2,24; 4,79</t>
+          <t>2,32; 4,64</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,43; 1,58</t>
+          <t>0,43; 1,53</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,71; 2,11</t>
+          <t>0,69; 2,03</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,0; 2,76</t>
+          <t>1,05; 2,68</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>2,17; 4,56</t>
+          <t>2,2; 4,47</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,48; 1,28</t>
+          <t>0,51; 1,34</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1,28; 2,5</t>
+          <t>1,3; 2,48</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1,01; 2,08</t>
+          <t>1,04; 2,14</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>2,48; 4,13</t>
+          <t>2,49; 4,12</t>
         </is>
       </c>
     </row>
@@ -1638,4 +1639,1622 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que padecen transtornos crónicos de la piel (tasa de respuesta: 99,82%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="n"/>
+      <c r="M1" s="3" t="n"/>
+      <c r="N1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Grupo I y II</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>1909</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>1177</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>2384</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>5024</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>598</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>1288</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>3599</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>4404</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>2507</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>2465</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>5983</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>9428</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>627; 5787</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>0; 4055</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>613; 5802</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>2224; 10014</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>0; 2985</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3944</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>1324; 7927</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>1699; 9395</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>637; 6279</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>646; 5771</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>2942; 10867</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>5096; 16059</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Grupo III</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>2184</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>3368</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>483</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>2421</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>2278</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>483</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>2184</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>2421</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>5647</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>673; 6403</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>1164; 7362</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>0; 2457</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>669; 6811</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>0; 6040</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>0; 2719</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>672; 5992</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>662; 7345</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>2457; 10798</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Grupo IV y V</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>778</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>2003</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>1236</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>1359</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>630</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>1392</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>1989</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>2137</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>2634</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>1392</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>3225</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>0; 5696</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>621; 5292</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>0; 5096</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4785</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3046</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4891</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>466; 5660</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>670; 5626</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>671; 5975</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4696</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>1230; 7761</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VI</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>587</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>4265</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>4198</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>6335</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>2041</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>2084</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>1361</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>7285</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>2628</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>6349</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>5559</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>13620</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>0; 2925</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>1810; 9438</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>2087; 8839</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>3071; 12645</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>648; 6743</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>617; 5474</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>0; 4806</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>3548; 13235</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>677; 5986</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>2640; 11487</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>2574; 10032</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>8427; 21938</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VII</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>718</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>3799</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>1454</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>3776</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>1292</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>2891</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>1326</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>4231</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>2011</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>6691</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>2780</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>8007</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>0; 3870</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>1440; 7866</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>0; 5131</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>1525; 8283</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>0; 4578</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>710; 6601</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>0; 4037</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>1933; 9820</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>618; 5999</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>3276; 12049</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>668; 6733</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>4599; 14607</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>No ha trabajado</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>1394</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>2894</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>636</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>2052</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>1944</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>1937</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>3409</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>1394</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>4837</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>2573</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>5460</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>0; 4948</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>723; 6647</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>0; 3173</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>0; 8402</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>457; 5716</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>629; 5873</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>897; 8183</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>0; 4318</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>2132; 9680</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>651; 6539</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>2288; 11441</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>5387</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>16322</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>8672</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>21791</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>5774</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>8838</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>12036</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>23597</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>11161</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>25160</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>20708</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>45387</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>2126; 10230</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>11062; 24502</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>4989; 14141</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>15227; 30532</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>2971; 10505</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>4928; 14493</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>7467; 19050</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>16481; 33511</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>6765; 17676</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>17983; 34453</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>14335; 29526</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>35047; 57892</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP1020-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP1020-Clase-trans_dic.xlsx
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,6; 5,55</t>
+          <t>0,6; 5,12</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,59</t>
+          <t>0,0; 4,24</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,74; 6,98</t>
+          <t>0,73; 7,37</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2,13; 9,59</t>
+          <t>2,07; 9,1</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,06</t>
+          <t>0,0; 3,24</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,39</t>
+          <t>0,0; 4,33</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,33; 7,94</t>
+          <t>1,36; 7,83</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1,24; 6,86</t>
+          <t>1,12; 6,68</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,32; 3,11</t>
+          <t>0,32; 3,09</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,36; 3,24</t>
+          <t>0,36; 3,47</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1,61; 5,94</t>
+          <t>1,52; 5,85</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>2,11; 6,65</t>
+          <t>2,14; 6,96</t>
         </is>
       </c>
     </row>
@@ -862,7 +862,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,73; 6,91</t>
+          <t>0,73; 6,77</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -872,12 +872,12 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,23; 7,78</t>
+          <t>1,08; 8,31</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,86</t>
+          <t>0,0; 2,87</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -887,32 +887,32 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,59; 6,04</t>
+          <t>0,59; 6,37</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,32</t>
+          <t>0,74; 7,08</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,57</t>
+          <t>0,0; 1,53</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,36; 3,17</t>
+          <t>0,36; 3,06</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,3; 3,36</t>
+          <t>0,3; 3,0</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,29; 5,68</t>
+          <t>1,4; 5,48</t>
         </is>
       </c>
     </row>
@@ -997,12 +997,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,45</t>
+          <t>0,0; 5,78</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,74; 6,28</t>
+          <t>0,74; 6,65</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -1012,47 +1012,47 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,83</t>
+          <t>0,0; 8,58</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,82</t>
+          <t>0,0; 4,77</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,51</t>
+          <t>0,0; 4,07</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,48</t>
+          <t>0,0; 5,64</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,73; 8,86</t>
+          <t>0,73; 9,18</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,4; 3,37</t>
+          <t>0,4; 3,77</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,39; 3,49</t>
+          <t>0,4; 3,85</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,42</t>
+          <t>0,0; 3,54</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1,06; 6,71</t>
+          <t>1,02; 6,57</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,46</t>
+          <t>0,0; 1,64</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,88; 4,59</t>
+          <t>0,85; 4,38</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,93; 3,95</t>
+          <t>0,74; 3,58</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,41; 5,8</t>
+          <t>1,36; 5,77</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,32; 3,34</t>
+          <t>0,32; 2,73</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,27; 2,41</t>
+          <t>0,28; 2,8</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,28</t>
+          <t>0,0; 2,6</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,63; 6,06</t>
+          <t>1,72; 6,19</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,17; 1,49</t>
+          <t>0,16; 1,61</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0,61; 2,66</t>
+          <t>0,65; 2,72</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,59; 2,31</t>
+          <t>0,62; 2,38</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1,93; 5,03</t>
+          <t>1,86; 4,81</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,72</t>
+          <t>0,0; 3,48</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,97; 5,27</t>
+          <t>1,07; 5,72</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,77</t>
+          <t>0,0; 3,57</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,28; 6,94</t>
+          <t>1,18; 7,23</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,6</t>
+          <t>0,0; 3,56</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,51; 4,72</t>
+          <t>0,54; 4,74</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,82</t>
+          <t>0,0; 2,9</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>1,19; 6,04</t>
+          <t>0,96; 6,23</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,27; 2,59</t>
+          <t>0,27; 2,23</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1,13; 4,17</t>
+          <t>1,15; 3,95</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,24; 2,41</t>
+          <t>0,24; 2,6</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>1,63; 5,18</t>
+          <t>1,4; 5,04</t>
         </is>
       </c>
     </row>
@@ -1417,22 +1417,22 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,61</t>
+          <t>0,0; 6,43</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1,34; 12,33</t>
+          <t>1,36; 13,14</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,19</t>
+          <t>0,0; 5,12</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,19</t>
+          <t>0,0; 10,48</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1442,37 +1442,37 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,62; 7,72</t>
+          <t>0,61; 7,92</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,93; 8,66</t>
+          <t>0,93; 7,66</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1,25; 11,36</t>
+          <t>1,38; 10,81</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,93</t>
+          <t>0,0; 3,05</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1,67; 7,57</t>
+          <t>1,63; 7,12</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0,5; 5,07</t>
+          <t>0,51; 5,12</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>1,62; 8,12</t>
+          <t>1,69; 8,5</t>
         </is>
       </c>
     </row>
@@ -1557,57 +1557,57 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,33; 1,6</t>
+          <t>0,33; 1,53</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,64; 3,63</t>
+          <t>1,58; 3,53</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,74; 2,11</t>
+          <t>0,74; 2,1</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2,32; 4,64</t>
+          <t>2,19; 4,73</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,43; 1,53</t>
+          <t>0,46; 1,65</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,69; 2,03</t>
+          <t>0,71; 2,02</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,05; 2,68</t>
+          <t>0,95; 2,61</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>2,2; 4,47</t>
+          <t>2,22; 4,47</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,51; 1,34</t>
+          <t>0,51; 1,29</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1,3; 2,48</t>
+          <t>1,34; 2,48</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1,04; 2,14</t>
+          <t>1,07; 2,08</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>627; 5787</t>
+          <t>628; 5343</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 4055</t>
+          <t>0; 3746</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>613; 5802</t>
+          <t>610; 6123</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2224; 10014</t>
+          <t>2165; 9507</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 2985</t>
+          <t>0; 3160</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 3944</t>
+          <t>0; 3885</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>1324; 7927</t>
+          <t>1353; 7816</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>1699; 9395</t>
+          <t>1532; 9149</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>637; 6279</t>
+          <t>637; 6243</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>646; 5771</t>
+          <t>647; 6192</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>2942; 10867</t>
+          <t>2779; 10697</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>5096; 16059</t>
+          <t>5159; 16790</t>
         </is>
       </c>
     </row>
@@ -2140,7 +2140,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>673; 6403</t>
+          <t>674; 6275</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -2150,12 +2150,12 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1164; 7362</t>
+          <t>1020; 7867</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 2457</t>
+          <t>0; 2471</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -2165,32 +2165,32 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>669; 6811</t>
+          <t>664; 7176</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 6040</t>
+          <t>703; 6762</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0; 2719</t>
+          <t>0; 2654</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>672; 5992</t>
+          <t>671; 5778</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>662; 7345</t>
+          <t>661; 6555</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>2457; 10798</t>
+          <t>2658; 10433</t>
         </is>
       </c>
     </row>
@@ -2343,12 +2343,12 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 5696</t>
+          <t>0; 3893</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>621; 5292</t>
+          <t>620; 5598</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -2358,47 +2358,47 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 5096</t>
+          <t>0; 4451</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 4785</t>
+          <t>0; 4741</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 3046</t>
+          <t>0; 3538</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 4891</t>
+          <t>0; 4258</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>466; 5660</t>
+          <t>465; 5863</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>670; 5626</t>
+          <t>672; 6281</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>671; 5975</t>
+          <t>679; 6589</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>0; 4696</t>
+          <t>0; 4860</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>1230; 7761</t>
+          <t>1180; 7605</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 2925</t>
+          <t>0; 3288</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1810; 9438</t>
+          <t>1741; 9007</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2087; 8839</t>
+          <t>1656; 8003</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3071; 12645</t>
+          <t>2972; 12587</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>648; 6743</t>
+          <t>649; 5524</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>617; 5474</t>
+          <t>626; 6360</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 4806</t>
+          <t>0; 5476</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>3548; 13235</t>
+          <t>3755; 13506</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>677; 5986</t>
+          <t>654; 6485</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>2640; 11487</t>
+          <t>2793; 11775</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>2574; 10032</t>
+          <t>2701; 10346</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>8427; 21938</t>
+          <t>8117; 20988</t>
         </is>
       </c>
     </row>
@@ -2759,62 +2759,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 3870</t>
+          <t>0; 3624</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>1440; 7866</t>
+          <t>1589; 8533</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0; 5131</t>
+          <t>0; 4867</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>1525; 8283</t>
+          <t>1415; 8631</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0; 4578</t>
+          <t>0; 4533</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>710; 6601</t>
+          <t>758; 6624</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>0; 4037</t>
+          <t>0; 4152</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>1933; 9820</t>
+          <t>1564; 10127</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>618; 5999</t>
+          <t>618; 5151</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>3276; 12049</t>
+          <t>3318; 11416</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>668; 6733</t>
+          <t>668; 7271</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>4599; 14607</t>
+          <t>3960; 14224</t>
         </is>
       </c>
     </row>
@@ -2967,22 +2967,22 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 4948</t>
+          <t>0; 4818</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>723; 6647</t>
+          <t>733; 7086</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0; 3173</t>
+          <t>0; 3128</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0; 8402</t>
+          <t>0; 7222</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2992,37 +2992,37 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>457; 5716</t>
+          <t>455; 5864</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>629; 5873</t>
+          <t>634; 5194</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>897; 8183</t>
+          <t>992; 7783</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0; 4318</t>
+          <t>0; 4489</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>2132; 9680</t>
+          <t>2088; 9110</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>651; 6539</t>
+          <t>652; 6598</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>2288; 11441</t>
+          <t>2383; 11971</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>2126; 10230</t>
+          <t>2081; 9784</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>11062; 24502</t>
+          <t>10652; 23771</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>4989; 14141</t>
+          <t>4997; 14129</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>15227; 30532</t>
+          <t>14374; 31083</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>2971; 10505</t>
+          <t>3118; 11287</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>4928; 14493</t>
+          <t>5095; 14446</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>7467; 19050</t>
+          <t>6761; 18504</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>16481; 33511</t>
+          <t>16628; 33466</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>6765; 17676</t>
+          <t>6717; 17074</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>17983; 34453</t>
+          <t>18618; 34474</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>14335; 29526</t>
+          <t>14767; 28787</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>35047; 57892</t>
+          <t>34978; 58020</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP1020-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP1020-Clase-trans_dic.xlsx
@@ -533,7 +533,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -649,42 +649,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>0,61%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>1,43%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>3,61%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>3,58%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>1,83%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>1,33%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>2,87%</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>4,81%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>0,61%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>1,43%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>3,61%</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>5,19%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>4,31%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,6; 5,12</t>
+          <t>0,0; 3,86</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,24</t>
+          <t>0,0; 5,06</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,73; 7,37</t>
+          <t>1,17; 8,1</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2,07; 9,1</t>
+          <t>1,3; 8,3</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,24</t>
+          <t>0,6; 4,96</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,33</t>
+          <t>0,0; 5,55</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,36; 7,83</t>
+          <t>0,76; 7,05</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1,12; 6,68</t>
+          <t>2,34; 10,42</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,32; 3,09</t>
+          <t>0,31; 3,15</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,36; 3,47</t>
+          <t>0,37; 3,57</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1,52; 5,85</t>
+          <t>1,59; 5,86</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>2,14; 6,96</t>
+          <t>2,37; 7,32</t>
         </is>
       </c>
     </row>
@@ -789,42 +789,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>0,56%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>2,15%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>2,38%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>2,36%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>3,56%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>0,56%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>2,15%</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>3,04%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>0,0; 3,04</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>0,73; 6,77</t>
-        </is>
-      </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
+          <t>0,59; 5,83</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>0,69; 5,98</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>1,08; 8,31</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 2,87</t>
-        </is>
-      </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
+          <t>0,72; 5,75</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>0,59; 6,37</t>
-        </is>
-      </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,74; 7,08</t>
+          <t>1,24; 8,44</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,53</t>
+          <t>0,0; 1,4</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,36; 3,06</t>
+          <t>0,36; 3,12</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,3; 3,0</t>
+          <t>0,3; 3,16</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,4; 5,48</t>
+          <t>1,37; 5,85</t>
         </is>
       </c>
     </row>
@@ -929,42 +929,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>1,37%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>0,73%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>1,84%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>3,16%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>1,15%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>2,38%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>2,38%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>1,37%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>0,73%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>1,84%</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,81%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,78</t>
+          <t>0,0; 4,81</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,74; 6,65</t>
+          <t>0,0; 3,66</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
+          <t>0,0; 6,37</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>0,64; 9,24</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 6,55</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>0,74; 6,91</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 8,58</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 4,77</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 4,07</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 5,64</t>
-        </is>
-      </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,73; 9,18</t>
+          <t>0,0; 8,65</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,4; 3,77</t>
+          <t>0,4; 3,6</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,4; 3,85</t>
+          <t>0,4; 3,63</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,54</t>
+          <t>0,0; 4,04</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1,02; 6,57</t>
+          <t>0,95; 6,75</t>
         </is>
       </c>
     </row>
@@ -1069,49 +1069,49 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>1,01%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>0,92%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0,65%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>3,53%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>0,29%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>2,07%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>1,88%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>2,91%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>1,01%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>0,92%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>3,68%</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>0,65%</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>3,34%</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>0,65%</t>
-        </is>
-      </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
           <t>1,47%</t>
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,6%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,64</t>
+          <t>0,32; 2,9</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,85; 4,38</t>
+          <t>0,27; 2,43</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,74; 3,58</t>
+          <t>0,0; 2,43</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,36; 5,77</t>
+          <t>1,6; 6,42</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,32; 2,73</t>
+          <t>0,0; 1,47</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,28; 2,8</t>
+          <t>0,85; 4,16</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,6</t>
+          <t>0,71; 3,59</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,72; 6,19</t>
+          <t>1,84; 6,84</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,16; 1,61</t>
+          <t>0,17; 1,68</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0,65; 2,72</t>
+          <t>0,78; 2,95</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,62; 2,38</t>
+          <t>0,59; 2,46</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1,86; 4,81</t>
+          <t>2,17; 5,48</t>
         </is>
       </c>
     </row>
@@ -1209,42 +1209,42 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>1,02%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>2,07%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>0,93%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>2,6%</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>0,69%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>2,55%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>1,07%</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>3,16%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>1,02%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>2,07%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>0,93%</t>
-        </is>
-      </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,76%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,48</t>
+          <t>0,0; 3,58</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,07; 5,72</t>
+          <t>0,52; 4,88</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,57</t>
+          <t>0,0; 3,14</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,18; 7,23</t>
+          <t>1,04; 6,03</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,56</t>
+          <t>0,0; 3,27</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,54; 4,74</t>
+          <t>0,93; 5,86</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,9</t>
+          <t>0,0; 3,66</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,96; 6,23</t>
+          <t>1,24; 6,88</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,27; 2,23</t>
+          <t>0,27; 2,44</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1,15; 3,95</t>
+          <t>1,11; 4,06</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,24; 2,6</t>
+          <t>0,24; 2,46</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>1,4; 5,04</t>
+          <t>1,38; 4,84</t>
         </is>
       </c>
     </row>
@@ -1349,42 +1349,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>2,63%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>2,86%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>5,02%</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>1,86%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>5,37%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>1,04%</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>2,98%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>2,63%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>2,86%</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>4,17%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,43</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1,36; 13,14</t>
+          <t>0,62; 7,15</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,12</t>
+          <t>0,93; 7,58</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,48</t>
+          <t>1,31; 11,81</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 6,22</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,61; 7,92</t>
+          <t>1,36; 12,47</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,93; 7,66</t>
+          <t>0,0; 5,33</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1,38; 10,81</t>
+          <t>0,0; 11,84</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,05</t>
+          <t>0,0; 3,23</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1,63; 7,12</t>
+          <t>1,55; 7,45</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0,51; 5,12</t>
+          <t>0,5; 4,53</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>1,69; 8,5</t>
+          <t>1,76; 8,73</t>
         </is>
       </c>
     </row>
@@ -1494,44 +1494,44 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
+          <t>1,24%</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>1,7%</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>3,3%</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>0,84%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
           <t>2,42%</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>1,29%</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>3,31%</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>3,64%</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>0,84%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>1,24%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>1,7%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>3,15%</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>0,84%</t>
-        </is>
-      </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
           <t>1,81%</t>
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,46%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,33; 1,53</t>
+          <t>0,43; 1,58</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,58; 3,53</t>
+          <t>0,71; 2,11</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,74; 2,1</t>
+          <t>1,0; 2,76</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2,19; 4,73</t>
+          <t>2,25; 4,78</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,46; 1,65</t>
+          <t>0,41; 1,59</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,71; 2,02</t>
+          <t>1,59; 3,56</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,95; 2,61</t>
+          <t>0,7; 2,05</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>2,22; 4,47</t>
+          <t>2,47; 5,21</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,51; 1,29</t>
+          <t>0,48; 1,28</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1,34; 2,48</t>
+          <t>1,28; 2,5</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1,07; 2,08</t>
+          <t>1,01; 2,08</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>2,49; 4,12</t>
+          <t>2,66; 4,39</t>
         </is>
       </c>
     </row>
@@ -1675,7 +1675,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1683,7 +1683,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -1791,42 +1791,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>7</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -1859,42 +1859,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>598</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>1288</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>3599</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>4387</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>1909</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>1177</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>2384</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>5024</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>598</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>1288</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>3599</t>
-        </is>
-      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>4404</t>
+          <t>5337</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>9428</t>
+          <t>9724</t>
         </is>
       </c>
     </row>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>628; 5343</t>
+          <t>0; 3762</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 3746</t>
+          <t>0; 4542</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>610; 6123</t>
+          <t>1172; 8085</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2165; 9507</t>
+          <t>1592; 10177</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 3160</t>
+          <t>627; 5175</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 3885</t>
+          <t>0; 4905</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>1353; 7816</t>
+          <t>629; 5858</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>1532; 9149</t>
+          <t>2410; 10722</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>637; 6243</t>
+          <t>634; 6364</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>647; 6192</t>
+          <t>651; 6353</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>2779; 10697</t>
+          <t>2903; 10720</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>5159; 16790</t>
+          <t>5353; 16496</t>
         </is>
       </c>
     </row>
@@ -1999,42 +1999,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="E7" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>5</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -2067,62 +2067,62 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>483</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>2421</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>2179</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>2184</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>3368</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>3528</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>483</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>2184</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>2421</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>2278</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>483</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>2184</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>2421</t>
-        </is>
-      </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>5647</t>
+          <t>5707</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>0; 2616</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>674; 6275</t>
-        </is>
-      </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
+          <t>663; 6568</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>634; 5470</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>1020; 7867</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>0; 2471</t>
-        </is>
-      </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
+          <t>672; 5333</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>664; 7176</t>
-        </is>
-      </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>703; 6762</t>
+          <t>1199; 8147</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0; 2654</t>
+          <t>0; 2433</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>671; 5778</t>
+          <t>673; 5893</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>661; 6555</t>
+          <t>661; 6913</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>2658; 10433</t>
+          <t>2571; 10990</t>
         </is>
       </c>
     </row>
@@ -2207,42 +2207,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -2275,62 +2275,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>1359</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>630</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>1392</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>1797</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>778</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>2003</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>1236</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>1359</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>630</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>1301</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>2137</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>2634</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>1392</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>1989</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>2137</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>2634</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>1392</t>
-        </is>
-      </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>3225</t>
+          <t>3098</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 3893</t>
+          <t>0; 4774</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>620; 5598</t>
+          <t>0; 3177</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
+          <t>0; 4806</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>363; 5262</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4411</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>626; 5818</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>0; 4451</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>0; 4741</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>0; 3538</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>0; 4258</t>
-        </is>
-      </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>465; 5863</t>
+          <t>0; 4627</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>672; 6281</t>
+          <t>673; 6004</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>679; 6589</t>
+          <t>688; 6208</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>0; 4860</t>
+          <t>0; 5542</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>1180; 7605</t>
+          <t>1047; 7451</t>
         </is>
       </c>
     </row>
@@ -2415,42 +2415,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>9</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -2483,42 +2483,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>2041</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>2084</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>1361</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>7122</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>587</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>4265</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>4198</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>6335</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>2041</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>2084</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>1361</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>7285</t>
+          <t>6581</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>13620</t>
+          <t>13703</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 3288</t>
+          <t>647; 5861</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1741; 9007</t>
+          <t>619; 5511</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1656; 8003</t>
+          <t>0; 5117</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2972; 12587</t>
+          <t>3240; 12967</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>649; 5524</t>
+          <t>0; 2944</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>626; 6360</t>
+          <t>1756; 8546</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 5476</t>
+          <t>1577; 8033</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>3755; 13506</t>
+          <t>3284; 12230</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>654; 6485</t>
+          <t>684; 6764</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>2793; 11775</t>
+          <t>3360; 12767</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>2701; 10346</t>
+          <t>2544; 10704</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>8117; 20988</t>
+          <t>8262; 20866</t>
         </is>
       </c>
     </row>
@@ -2623,32 +2623,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>6</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -2691,42 +2691,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>1292</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>2891</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>1326</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>3851</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
           <t>718</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>3799</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="I17" s="2" t="inlineStr">
         <is>
           <t>1454</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>3776</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>1292</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>2891</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>1326</t>
-        </is>
-      </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>4231</t>
+          <t>3511</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>8007</t>
+          <t>7363</t>
         </is>
       </c>
     </row>
@@ -2759,62 +2759,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 3624</t>
+          <t>0; 4552</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>1589; 8533</t>
+          <t>722; 6827</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0; 4867</t>
+          <t>0; 4492</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>1415; 8631</t>
+          <t>1537; 8941</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0; 4533</t>
+          <t>0; 3406</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>758; 6624</t>
+          <t>1383; 8736</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>0; 4152</t>
+          <t>0; 4988</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>1564; 10127</t>
+          <t>1468; 8165</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>618; 5151</t>
+          <t>617; 5637</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>3318; 11416</t>
+          <t>3199; 11728</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>668; 7271</t>
+          <t>661; 6863</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>3960; 14224</t>
+          <t>3695; 12918</t>
         </is>
       </c>
     </row>
@@ -2831,42 +2831,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="H19" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="I19" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="J19" s="2" t="inlineStr">
         <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -2899,42 +2899,42 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>1944</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>1937</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>3431</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
           <t>1394</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>2894</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="I20" s="2" t="inlineStr">
         <is>
           <t>636</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>2052</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>1944</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>1937</t>
-        </is>
-      </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>3409</t>
+          <t>2345</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>5460</t>
+          <t>5776</t>
         </is>
       </c>
     </row>
@@ -2967,62 +2967,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 4818</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>733; 7086</t>
+          <t>459; 5292</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0; 3128</t>
+          <t>628; 5141</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0; 7222</t>
+          <t>894; 8062</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 4658</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>455; 5864</t>
+          <t>731; 6720</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>634; 5194</t>
+          <t>0; 3257</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>992; 7783</t>
+          <t>0; 8333</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0; 4489</t>
+          <t>0; 4757</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>2088; 9110</t>
+          <t>1978; 9533</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>652; 6598</t>
+          <t>647; 5844</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>2383; 11971</t>
+          <t>2436; 12110</t>
         </is>
       </c>
     </row>
@@ -3039,42 +3039,42 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="I22" s="2" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="J22" s="2" t="inlineStr">
         <is>
           <t>31</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
@@ -3107,42 +3107,42 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>5774</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>8838</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>12036</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>22767</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
           <t>5387</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>16322</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="I23" s="2" t="inlineStr">
         <is>
           <t>8672</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>21791</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>5774</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>8838</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>12036</t>
-        </is>
-      </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>23597</t>
+          <t>22603</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3162,7 +3162,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>45387</t>
+          <t>45370</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>2081; 9784</t>
+          <t>2943; 10833</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>10652; 23771</t>
+          <t>5036; 15027</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>4997; 14129</t>
+          <t>7065; 19598</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>14374; 31083</t>
+          <t>15526; 32926</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>3118; 11287</t>
+          <t>2609; 10188</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>5095; 14446</t>
+          <t>10751; 24006</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>6761; 18504</t>
+          <t>4683; 13792</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>16628; 33466</t>
+          <t>15324; 32373</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>6717; 17074</t>
+          <t>6355; 16896</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>18618; 34474</t>
+          <t>17816; 34752</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>14767; 28787</t>
+          <t>14009; 28779</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>34978; 58020</t>
+          <t>34860; 57536</t>
         </is>
       </c>
     </row>
